--- a/DATA CLEANING & ESSENTIAL 1.xlsx
+++ b/DATA CLEANING & ESSENTIAL 1.xlsx
@@ -10578,7 +10578,7 @@
     <row r="29" spans="3:5" ht="15.75" customHeight="1">
       <c r="C29" s="18">
         <f ca="1">NOW()</f>
-        <v>46188.542944560184</v>
+        <v>46188.566429050923</v>
       </c>
     </row>
     <row r="30" spans="3:5" ht="15.75" customHeight="1">
@@ -10607,7 +10607,7 @@
       <c r="D34" s="11" t="str">
         <f ca="1">TEXT(NOW(),"mm/dd/yyyy") &amp; CHAR(10) &amp; TEXT(NOW(),"hh:mm AM/PM")</f>
         <v>06/15/2026
-01:01 PM</v>
+01:35 PM</v>
       </c>
     </row>
     <row r="35" spans="3:5" ht="15.75" customHeight="1">
